--- a/LocalHost/courses/BCJ Challenge2026/info/Documents/Equipes et Duo.xlsx
+++ b/LocalHost/courses/BCJ Challenge2026/info/Documents/Equipes et Duo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t xml:space="preserve">Nom équipe</t>
   </si>
@@ -1315,13 +1315,175 @@
   </si>
   <si>
     <t>Chevenez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSS Team JURA </t>
+  </si>
+  <si>
+    <t>Tico </t>
+  </si>
+  <si>
+    <t>Luka </t>
+  </si>
+  <si>
+    <t>Delémont </t>
+  </si>
+  <si>
+    <t xml:space="preserve">catégorie équipe pas entreprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Luca </t>
+  </si>
+  <si>
+    <t>Mirco </t>
+  </si>
+  <si>
+    <t>Courtételle </t>
+  </si>
+  <si>
+    <t>Menozzi </t>
+  </si>
+  <si>
+    <t>Marc </t>
+  </si>
+  <si>
+    <t>Raval </t>
+  </si>
+  <si>
+    <t>Julien </t>
+  </si>
+  <si>
+    <t>Courtedoux </t>
+  </si>
+  <si>
+    <t>Ferrara</t>
+  </si>
+  <si>
+    <t>Agostino </t>
+  </si>
+  <si>
+    <t>Glovelier </t>
+  </si>
+  <si>
+    <t>Cecconi </t>
+  </si>
+  <si>
+    <t>Leornardo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est déjà inscrit, juste le rajouter à l'équipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divtec TEAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Miserez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déja inscrit juste intégrer l'équipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude Fahrni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Escribano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virginie Plumez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divtec TEAM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cédric Erard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luc Chappuis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Plumez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bastien Lièvre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidag Jura </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coureur 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berret </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coline </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Courroux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coureur 2 </t>
+  </si>
+  <si>
+    <t>Guillaume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coureur 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallimann </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loris </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAG HEUER</t>
+  </si>
+  <si>
+    <t>HALM</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>Brevilliers</t>
+  </si>
+  <si>
+    <t>GIRARD</t>
+  </si>
+  <si>
+    <t>Thibault</t>
+  </si>
+  <si>
+    <t>Montreux-Château</t>
+  </si>
+  <si>
+    <t>RIFFAULT</t>
+  </si>
+  <si>
+    <t>Nathan</t>
+  </si>
+  <si>
+    <t>Thiancourt</t>
+  </si>
+  <si>
+    <t>FETSCHER</t>
+  </si>
+  <si>
+    <t>Stève</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duo mixte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Boélons</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -1361,12 +1523,16 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <color indexed="64"/>
+      <sz val="9.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7.500000"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1409,10 +1575,23 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="13">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1556,63 +1735,11 @@
       </bottom>
       <diagonal style="none"/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="none"/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="none"/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
@@ -1788,18 +1915,20 @@
     <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="5" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="8" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="8" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="8" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf fontId="0" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2318,7 +2447,8 @@
     <col bestFit="1" min="7" max="7" width="24.06640625"/>
     <col bestFit="1" min="8" max="8" width="5"/>
     <col customWidth="1" min="11" max="11" width="14.59765625"/>
-    <col bestFit="1" customWidth="1" min="12" max="12" width="59.6640625"/>
+    <col customWidth="1" min="12" max="12" width="16"/>
+    <col customWidth="1" min="13" max="13" width="38.265625"/>
     <col customWidth="1" min="14" max="14" width="33.59765625"/>
   </cols>
   <sheetData>
@@ -7009,23 +7139,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" ht="14.25">
-      <c r="A171" t="s">
+    <row r="171">
+      <c r="A171" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="D171" s="65" t="s">
+      <c r="D171" s="58" t="s">
         <v>280</v>
       </c>
-      <c r="E171" s="66" t="s">
+      <c r="E171" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="F171" s="66">
+      <c r="F171" s="26">
         <v>2900</v>
       </c>
-      <c r="G171" s="66" t="s">
+      <c r="G171" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="H171" s="65">
+      <c r="H171" s="58">
         <v>1993</v>
       </c>
       <c r="I171" s="33" t="s">
@@ -7038,23 +7168,23 @@
         <v>244</v>
       </c>
     </row>
-    <row r="172" ht="14.25">
-      <c r="A172" t="s">
+    <row r="172">
+      <c r="A172" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="D172" s="67" t="s">
+      <c r="D172" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="E172" s="68" t="s">
+      <c r="E172" s="31" t="s">
         <v>431</v>
       </c>
-      <c r="F172" s="68">
+      <c r="F172" s="31">
         <v>2906</v>
       </c>
-      <c r="G172" s="68" t="s">
+      <c r="G172" s="31" t="s">
         <v>432</v>
       </c>
-      <c r="H172" s="67">
+      <c r="H172" s="46">
         <v>1969</v>
       </c>
       <c r="I172" s="28" t="s">
@@ -7065,6 +7195,539 @@
       </c>
       <c r="K172" s="40" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="19"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C174" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="E174" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="F174" s="26">
+        <v>2800</v>
+      </c>
+      <c r="G174" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="H174" s="26">
+        <v>2000</v>
+      </c>
+      <c r="I174" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="23">
+        <v>4</v>
+      </c>
+      <c r="K174" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C175" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D175" s="31" t="s">
+        <v>438</v>
+      </c>
+      <c r="E175" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="F175" s="31">
+        <v>2852</v>
+      </c>
+      <c r="G175" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="H175" s="31">
+        <v>1983</v>
+      </c>
+      <c r="I175" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J175" s="23">
+        <v>4</v>
+      </c>
+      <c r="K175" s="24" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C176" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D176" s="31" t="s">
+        <v>441</v>
+      </c>
+      <c r="E176" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="F176" s="31">
+        <v>2800</v>
+      </c>
+      <c r="G176" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H176" s="31">
+        <v>1989</v>
+      </c>
+      <c r="I176" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J176" s="23">
+        <v>4</v>
+      </c>
+      <c r="K176" s="24" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C177" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D177" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="E177" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="F177" s="31">
+        <v>2905</v>
+      </c>
+      <c r="G177" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="H177" s="31">
+        <v>1980</v>
+      </c>
+      <c r="I177" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" s="23">
+        <v>4</v>
+      </c>
+      <c r="K177" s="24" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C178" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D178" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="E178" s="31" t="s">
+        <v>447</v>
+      </c>
+      <c r="F178" s="31">
+        <v>2855</v>
+      </c>
+      <c r="G178" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="H178" s="31">
+        <v>1969</v>
+      </c>
+      <c r="I178" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J178" s="23">
+        <v>4</v>
+      </c>
+      <c r="K178" s="24" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C179" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D179" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="E179" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="F179" s="31">
+        <v>2800</v>
+      </c>
+      <c r="G179" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="H179" s="31">
+        <v>1975</v>
+      </c>
+      <c r="I179" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="23">
+        <v>4</v>
+      </c>
+      <c r="K179" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="M179" s="65" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="19"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="C181" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" s="66" t="s">
+        <v>453</v>
+      </c>
+      <c r="G181" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="19"/>
+      <c r="C182" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" s="66" t="s">
+        <v>455</v>
+      </c>
+      <c r="G182" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="19"/>
+      <c r="C183" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D183" s="66" t="s">
+        <v>456</v>
+      </c>
+      <c r="G183" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="19"/>
+      <c r="C184" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D184" t="s">
+        <v>457</v>
+      </c>
+      <c r="G184" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="19"/>
+      <c r="G185" s="24"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="67" t="s">
+        <v>458</v>
+      </c>
+      <c r="C186" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" t="s">
+        <v>459</v>
+      </c>
+      <c r="G186" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="19"/>
+      <c r="C187" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187" t="s">
+        <v>460</v>
+      </c>
+      <c r="G187" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="19"/>
+      <c r="C188" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D188" s="66" t="s">
+        <v>461</v>
+      </c>
+      <c r="G188" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="19"/>
+      <c r="C189" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D189" t="s">
+        <v>462</v>
+      </c>
+      <c r="G189" s="40" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="68" t="s">
+        <v>463</v>
+      </c>
+      <c r="C191" s="69" t="s">
+        <v>464</v>
+      </c>
+      <c r="D191" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="E191" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="F191" s="23">
+        <v>2822</v>
+      </c>
+      <c r="G191" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="H191" s="23">
+        <v>2000</v>
+      </c>
+      <c r="I191" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="J191" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="68" t="s">
+        <v>463</v>
+      </c>
+      <c r="C192" s="69" t="s">
+        <v>468</v>
+      </c>
+      <c r="D192" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="E192" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="F192" s="23">
+        <v>2906</v>
+      </c>
+      <c r="G192" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="H192" s="23">
+        <v>1989</v>
+      </c>
+      <c r="I192" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J192" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="68" t="s">
+        <v>463</v>
+      </c>
+      <c r="C193" s="69" t="s">
+        <v>470</v>
+      </c>
+      <c r="D193" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="E193" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="F193" s="23">
+        <v>2900</v>
+      </c>
+      <c r="G193" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="H193" s="23">
+        <v>1997</v>
+      </c>
+      <c r="I193" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J193" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" ht="14.25">
+      <c r="A194" s="70"/>
+    </row>
+    <row r="195" ht="14.25">
+      <c r="A195" s="70" t="s">
+        <v>473</v>
+      </c>
+      <c r="C195" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195" s="39" t="s">
+        <v>474</v>
+      </c>
+      <c r="E195" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="F195" s="27">
+        <v>70400</v>
+      </c>
+      <c r="G195" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="H195" s="27">
+        <v>1987</v>
+      </c>
+      <c r="I195" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="J195" s="37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" ht="14.25">
+      <c r="A196" s="70" t="s">
+        <v>473</v>
+      </c>
+      <c r="C196" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D196" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="E196" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="F196" s="32">
+        <v>90130</v>
+      </c>
+      <c r="G196" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="H196" s="32">
+        <v>1992</v>
+      </c>
+      <c r="I196" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J196" s="38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" ht="14.25">
+      <c r="A197" s="70" t="s">
+        <v>473</v>
+      </c>
+      <c r="C197" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D197" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="E197" s="30" t="s">
+        <v>481</v>
+      </c>
+      <c r="F197" s="32">
+        <v>90100</v>
+      </c>
+      <c r="G197" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="H197" s="32">
+        <v>1998</v>
+      </c>
+      <c r="I197" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" ht="14.25">
+      <c r="A198" s="70" t="s">
+        <v>473</v>
+      </c>
+      <c r="C198" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D198" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="E198" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="F198" s="32">
+        <v>90100</v>
+      </c>
+      <c r="G198" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H198" s="32">
+        <v>1981</v>
+      </c>
+      <c r="I198" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" ht="14.25">
+      <c r="A200" s="70">
+        <v>489</v>
+      </c>
+      <c r="C200" t="s">
+        <v>485</v>
+      </c>
+      <c r="D200" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="201" ht="14.25">
+      <c r="A201" s="70">
+        <v>490</v>
+      </c>
+      <c r="C201" t="s">
+        <v>485</v>
+      </c>
+      <c r="D201" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
